--- a/data/biomass/biomass_shoots.xlsx
+++ b/data/biomass/biomass_shoots.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://texastechuniversity-my.sharepoint.com/personal/monikell_ttu_edu/Documents/0_sorted_files/research/mk/exp_02/data/biomass/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrkel\Documents\git\2025_g34p\data\biomass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="976" documentId="8_{F21C694C-6164-454A-875A-D2F7FD2B435B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2889E583-185B-494A-962D-BD70E74F96AB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06D577C-2FAF-419C-97D5-E1557F0D96CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{7C2F5384-3529-46A3-A3B9-88FF292BE176}"/>
+    <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{7C2F5384-3529-46A3-A3B9-88FF292BE176}"/>
   </bookViews>
   <sheets>
     <sheet name="biomass_shoots" sheetId="1" r:id="rId1"/>
@@ -51,9 +51,6 @@
     <t>individual</t>
   </si>
   <si>
-    <t>biomass_shoots</t>
-  </si>
-  <si>
     <t>notes</t>
   </si>
   <si>
@@ -64,6 +61,9 @@
   </si>
   <si>
     <t>only one with an MIA sticker</t>
+  </si>
+  <si>
+    <t>biomass_shoots_g</t>
   </si>
 </sst>
 </file>
@@ -968,14 +968,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EFF3E9B-147D-4957-B386-0058A7C6B06B}">
   <dimension ref="A1:E384"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -986,18 +986,18 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1006,12 +1006,12 @@
         <v>3.4729999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1020,12 +1020,12 @@
         <v>3.0708000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1034,12 +1034,12 @@
         <v>3.2833999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1048,12 +1048,12 @@
         <v>5.2859999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1062,12 +1062,12 @@
         <v>6.4976000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1076,12 +1076,12 @@
         <v>7.0534999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1090,12 +1090,12 @@
         <v>4.3235999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1104,12 +1104,12 @@
         <v>4.1006</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1118,12 +1118,12 @@
         <v>5.8723999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1132,12 +1132,12 @@
         <v>9.1559000000000008</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1146,12 +1146,12 @@
         <v>8.1532999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1160,12 +1160,12 @@
         <v>16.232600000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1174,12 +1174,12 @@
         <v>7.4766000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1188,12 +1188,12 @@
         <v>13.672000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1202,12 +1202,12 @@
         <v>7.0301999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1216,12 +1216,12 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1230,12 +1230,12 @@
         <v>5.8924000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1244,12 +1244,12 @@
         <v>6.7683999999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1258,12 +1258,12 @@
         <v>9.2538</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1272,12 +1272,12 @@
         <v>11.505699999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1286,12 +1286,12 @@
         <v>7.2698</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1300,12 +1300,12 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1314,12 +1314,12 @@
         <v>5.3638000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1328,12 +1328,12 @@
         <v>3.3837999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1342,12 +1342,12 @@
         <v>9.1862999999999992</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1356,12 +1356,12 @@
         <v>9.2463999999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1370,12 +1370,12 @@
         <v>9.3671000000000006</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1384,12 +1384,12 @@
         <v>8.0518000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1398,12 +1398,12 @@
         <v>6.9252000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1412,12 +1412,12 @@
         <v>12.866199999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1426,12 +1426,12 @@
         <v>5.367</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1440,12 +1440,12 @@
         <v>7.1478999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1454,12 +1454,12 @@
         <v>0.30740000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1468,12 +1468,12 @@
         <v>1.1958</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1482,12 +1482,12 @@
         <v>3.5291999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1496,12 +1496,12 @@
         <v>1.008</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>54</v>
       </c>
       <c r="B38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1510,12 +1510,12 @@
         <v>3.7250999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1524,12 +1524,12 @@
         <v>2.9317000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1538,12 +1538,12 @@
         <v>0.24299999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>84</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1552,12 +1552,12 @@
         <v>0.65769999999999995</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1566,12 +1566,12 @@
         <v>0.28060000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1580,12 +1580,12 @@
         <v>0.52029999999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1594,12 +1594,12 @@
         <v>5.9132999999999996</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>15</v>
       </c>
       <c r="B45" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1608,12 +1608,12 @@
         <v>0.98350000000000004</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>83</v>
       </c>
       <c r="B46" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1622,12 +1622,12 @@
         <v>4.4282000000000004</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1636,12 +1636,12 @@
         <v>4.8183999999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1650,12 +1650,12 @@
         <v>1.1013999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>77</v>
       </c>
       <c r="B49" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1664,12 +1664,12 @@
         <v>1.2036</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>18</v>
       </c>
       <c r="B50" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1678,12 +1678,12 @@
         <v>0.2384</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>19</v>
       </c>
       <c r="B51" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1692,12 +1692,12 @@
         <v>1.7697000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1706,12 +1706,12 @@
         <v>6.2081999999999997</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>20</v>
       </c>
       <c r="B53" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1720,12 +1720,12 @@
         <v>0.5857</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>73</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1734,12 +1734,12 @@
         <v>3.7736000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1748,12 +1748,12 @@
         <v>5.5358000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>21</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1762,12 +1762,12 @@
         <v>8.8499999999999995E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1776,12 +1776,12 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1790,12 +1790,12 @@
         <v>0.75860000000000005</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1804,12 +1804,12 @@
         <v>0.34300000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>23</v>
       </c>
       <c r="B60" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1818,12 +1818,12 @@
         <v>5.6078999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1832,12 +1832,12 @@
         <v>1.3607</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>87</v>
       </c>
       <c r="B62" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1846,12 +1846,12 @@
         <v>5.0726000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1860,12 +1860,12 @@
         <v>2.9477000000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>26</v>
       </c>
       <c r="B64" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1874,12 +1874,12 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1888,12 +1888,12 @@
         <v>0.70440000000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>28</v>
       </c>
       <c r="B66" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1902,12 +1902,12 @@
         <v>3.8586</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>29</v>
       </c>
       <c r="B67" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1916,12 +1916,12 @@
         <v>2.9550999999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>70</v>
       </c>
       <c r="B68" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1930,12 +1930,12 @@
         <v>3.371</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>97</v>
       </c>
       <c r="B69" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1944,12 +1944,12 @@
         <v>8.8228000000000009</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1958,12 +1958,12 @@
         <v>6.5990000000000002</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>91</v>
       </c>
       <c r="B71" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1972,12 +1972,12 @@
         <v>5.9340000000000002</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1986,12 +1986,12 @@
         <v>6.8739999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>96</v>
       </c>
       <c r="B73" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -2000,12 +2000,12 @@
         <v>3.0259999999999998</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>89</v>
       </c>
       <c r="B74" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2014,12 +2014,12 @@
         <v>9.9533000000000005</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>66</v>
       </c>
       <c r="B75" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2028,12 +2028,12 @@
         <v>8.8996999999999993</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>31</v>
       </c>
       <c r="B76" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2042,12 +2042,12 @@
         <v>9.9855999999999998</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>68</v>
       </c>
       <c r="B77" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2056,12 +2056,12 @@
         <v>12.6379</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>74</v>
       </c>
       <c r="B78" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2070,12 +2070,12 @@
         <v>7.4798</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>94</v>
       </c>
       <c r="B79" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2084,12 +2084,12 @@
         <v>11.4549</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>32</v>
       </c>
       <c r="B80" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2098,12 +2098,12 @@
         <v>1.8366</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>92</v>
       </c>
       <c r="B81" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2112,12 +2112,12 @@
         <v>6.6261999999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2126,12 +2126,12 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>72</v>
       </c>
       <c r="B83" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2140,12 +2140,12 @@
         <v>9.8059999999999992</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>69</v>
       </c>
       <c r="B84" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2154,12 +2154,12 @@
         <v>7.4931999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>34</v>
       </c>
       <c r="B85" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2168,12 +2168,12 @@
         <v>10.9246</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>76</v>
       </c>
       <c r="B86" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2182,12 +2182,12 @@
         <v>7.3590999999999998</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2196,12 +2196,12 @@
         <v>11.313800000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>79</v>
       </c>
       <c r="B88" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2210,12 +2210,12 @@
         <v>1.0447</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>35</v>
       </c>
       <c r="B89" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2224,12 +2224,12 @@
         <v>3.0394000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2238,12 +2238,12 @@
         <v>6.1958000000000002</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>99</v>
       </c>
       <c r="B91" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2252,12 +2252,12 @@
         <v>6.5605000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>71</v>
       </c>
       <c r="B92" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2266,12 +2266,12 @@
         <v>11.912800000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>36</v>
       </c>
       <c r="B93" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2280,12 +2280,12 @@
         <v>12.638999999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2294,12 +2294,12 @@
         <v>6.3949999999999996</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>37</v>
       </c>
       <c r="B95" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2308,12 +2308,12 @@
         <v>11.504099999999999</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>81</v>
       </c>
       <c r="B96" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2322,12 +2322,12 @@
         <v>6.1189999999999998</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>38</v>
       </c>
       <c r="B97" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2336,12 +2336,12 @@
         <v>5.7565999999999997</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>39</v>
       </c>
       <c r="B98" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C98">
         <v>97</v>
@@ -2350,12 +2350,12 @@
         <v>0.61209999999999998</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>90</v>
       </c>
       <c r="B99" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C99">
         <v>98</v>
@@ -2364,12 +2364,12 @@
         <v>0.48209999999999997</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>75</v>
       </c>
       <c r="B100" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C100">
         <v>99</v>
@@ -2378,12 +2378,12 @@
         <v>3.8854000000000002</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>117</v>
       </c>
       <c r="B101" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C101">
         <v>100</v>
@@ -2392,12 +2392,12 @@
         <v>0.71789999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>145</v>
       </c>
       <c r="B102" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C102">
         <v>101</v>
@@ -2406,12 +2406,12 @@
         <v>3.2923</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>138</v>
       </c>
       <c r="B103" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C103">
         <v>102</v>
@@ -2420,12 +2420,12 @@
         <v>3.1116999999999999</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>101</v>
       </c>
       <c r="B104" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C104">
         <v>103</v>
@@ -2434,12 +2434,12 @@
         <v>0.13539999999999999</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>125</v>
       </c>
       <c r="B105" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C105">
         <v>104</v>
@@ -2448,12 +2448,12 @@
         <v>0.68269999999999997</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>148</v>
       </c>
       <c r="B106" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C106">
         <v>105</v>
@@ -2462,12 +2462,12 @@
         <v>0.25850000000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>115</v>
       </c>
       <c r="B107" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C107">
         <v>106</v>
@@ -2476,12 +2476,12 @@
         <v>0.374</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C108">
         <v>107</v>
@@ -2490,12 +2490,12 @@
         <v>4.5641999999999996</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>126</v>
       </c>
       <c r="B109" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C109">
         <v>108</v>
@@ -2504,12 +2504,12 @@
         <v>4.0469999999999997</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>129</v>
       </c>
       <c r="B110" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C110">
         <v>109</v>
@@ -2518,12 +2518,12 @@
         <v>4.7777000000000003</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>162</v>
       </c>
       <c r="B111" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C111">
         <v>110</v>
@@ -2532,12 +2532,12 @@
         <v>5.6761999999999997</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C112">
         <v>111</v>
@@ -2546,12 +2546,12 @@
         <v>1.2602</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>107</v>
       </c>
       <c r="B113" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C113">
         <v>112</v>
@@ -2560,12 +2560,12 @@
         <v>1.2584</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>147</v>
       </c>
       <c r="B114" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C114">
         <v>113</v>
@@ -2574,12 +2574,12 @@
         <v>0.7591</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>128</v>
       </c>
       <c r="B115" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115">
         <v>114</v>
@@ -2588,12 +2588,12 @@
         <v>0.56030000000000002</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>169</v>
       </c>
       <c r="B116" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C116">
         <v>115</v>
@@ -2602,12 +2602,12 @@
         <v>9.2857000000000003</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>105</v>
       </c>
       <c r="B117" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C117">
         <v>116</v>
@@ -2616,12 +2616,12 @@
         <v>0.98670000000000002</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>140</v>
       </c>
       <c r="B118" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118">
         <v>117</v>
@@ -2630,12 +2630,12 @@
         <v>3.5750000000000002</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>163</v>
       </c>
       <c r="B119" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C119">
         <v>118</v>
@@ -2644,12 +2644,12 @@
         <v>6.2868000000000004</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>120</v>
       </c>
       <c r="B120" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C120">
         <v>119</v>
@@ -2658,12 +2658,12 @@
         <v>0.61509999999999998</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>139</v>
       </c>
       <c r="B121" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C121">
         <v>120</v>
@@ -2672,12 +2672,12 @@
         <v>0.43530000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>142</v>
       </c>
       <c r="B122" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C122">
         <v>121</v>
@@ -2686,12 +2686,12 @@
         <v>0.3422</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>114</v>
       </c>
       <c r="B123" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C123">
         <v>122</v>
@@ -2700,12 +2700,12 @@
         <v>0.93489999999999995</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>175</v>
       </c>
       <c r="B124" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C124">
         <v>123</v>
@@ -2714,12 +2714,12 @@
         <v>7.2286000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C125">
         <v>124</v>
@@ -2728,12 +2728,12 @@
         <v>1.8342000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>103</v>
       </c>
       <c r="B126" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C126">
         <v>125</v>
@@ -2742,12 +2742,12 @@
         <v>3.7616000000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>165</v>
       </c>
       <c r="B127" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C127">
         <v>126</v>
@@ -2756,12 +2756,12 @@
         <v>4.6938000000000004</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>143</v>
       </c>
       <c r="B128" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C128">
         <v>127</v>
@@ -2770,12 +2770,12 @@
         <v>0.77859999999999996</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>146</v>
       </c>
       <c r="B129" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C129">
         <v>128</v>
@@ -2784,12 +2784,12 @@
         <v>1.024</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>127</v>
       </c>
       <c r="B130" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C130">
         <v>129</v>
@@ -2798,12 +2798,12 @@
         <v>2.2410000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>112</v>
       </c>
       <c r="B131" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C131">
         <v>130</v>
@@ -2812,12 +2812,12 @@
         <v>2.6833999999999998</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>123</v>
       </c>
       <c r="B132" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C132">
         <v>131</v>
@@ -2826,12 +2826,12 @@
         <v>2.6351</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>171</v>
       </c>
       <c r="B133" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C133">
         <v>132</v>
@@ -2840,12 +2840,12 @@
         <v>5.0349000000000004</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>159</v>
       </c>
       <c r="B134" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C134">
         <v>133</v>
@@ -2854,12 +2854,12 @@
         <v>5.3715999999999999</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>173</v>
       </c>
       <c r="B135" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C135">
         <v>134</v>
@@ -2868,12 +2868,12 @@
         <v>4.5532000000000004</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>176</v>
       </c>
       <c r="B136" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C136">
         <v>135</v>
@@ -2882,12 +2882,12 @@
         <v>5.9615999999999998</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>132</v>
       </c>
       <c r="B137" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C137">
         <v>136</v>
@@ -2896,12 +2896,12 @@
         <v>2.1501999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>174</v>
       </c>
       <c r="B138" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C138">
         <v>137</v>
@@ -2910,12 +2910,12 @@
         <v>7.2447999999999997</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>130</v>
       </c>
       <c r="B139" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C139">
         <v>138</v>
@@ -2924,12 +2924,12 @@
         <v>6.7702</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C140">
         <v>139</v>
@@ -2938,12 +2938,12 @@
         <v>9.8584999999999994</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>157</v>
       </c>
       <c r="B141" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C141">
         <v>140</v>
@@ -2952,12 +2952,12 @@
         <v>10.356</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>291</v>
       </c>
       <c r="B142" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C142">
         <v>141</v>
@@ -2966,12 +2966,12 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>166</v>
       </c>
       <c r="B143" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C143">
         <v>142</v>
@@ -2980,12 +2980,12 @@
         <v>12.7225</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>297</v>
       </c>
       <c r="B144" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C144">
         <v>143</v>
@@ -2994,12 +2994,12 @@
         <v>6.7766000000000002</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>288</v>
       </c>
       <c r="B145" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C145">
         <v>144</v>
@@ -3008,12 +3008,12 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>110</v>
       </c>
       <c r="B146" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C146">
         <v>145</v>
@@ -3022,12 +3022,12 @@
         <v>7.0732999999999997</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>111</v>
       </c>
       <c r="B147" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C147">
         <v>146</v>
@@ -3036,12 +3036,12 @@
         <v>2.5859999999999999</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>289</v>
       </c>
       <c r="B148" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C148">
         <v>147</v>
@@ -3050,12 +3050,12 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>189</v>
       </c>
       <c r="B149" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C149">
         <v>148</v>
@@ -3064,12 +3064,12 @@
         <v>15.63</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>287</v>
       </c>
       <c r="B150" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C150">
         <v>149</v>
@@ -3078,12 +3078,12 @@
         <v>8.4600000000000009</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>296</v>
       </c>
       <c r="B151" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C151">
         <v>150</v>
@@ -3092,12 +3092,12 @@
         <v>10.55</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>276</v>
       </c>
       <c r="B152" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C152">
         <v>151</v>
@@ -3106,12 +3106,12 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>290</v>
       </c>
       <c r="B153" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C153">
         <v>152</v>
@@ -3120,12 +3120,12 @@
         <v>7.83</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>131</v>
       </c>
       <c r="B154" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C154">
         <v>153</v>
@@ -3134,12 +3134,12 @@
         <v>7.3765000000000001</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>158</v>
       </c>
       <c r="B155" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C155">
         <v>154</v>
@@ -3148,12 +3148,12 @@
         <v>5.8719000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>118</v>
       </c>
       <c r="B156" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C156">
         <v>155</v>
@@ -3162,12 +3162,12 @@
         <v>8.9669000000000008</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>102</v>
       </c>
       <c r="B157" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C157">
         <v>156</v>
@@ -3176,12 +3176,12 @@
         <v>10.4429</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>294</v>
       </c>
       <c r="B158" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C158">
         <v>157</v>
@@ -3190,12 +3190,12 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>292</v>
       </c>
       <c r="B159" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C159">
         <v>158</v>
@@ -3204,12 +3204,12 @@
         <v>10.68</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>283</v>
       </c>
       <c r="B160" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C160">
         <v>159</v>
@@ -3218,12 +3218,12 @@
         <v>8.32</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>293</v>
       </c>
       <c r="B161" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C161">
         <v>160</v>
@@ -3232,12 +3232,12 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>121</v>
       </c>
       <c r="B162" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C162">
         <v>161</v>
@@ -3246,12 +3246,12 @@
         <v>0.52929999999999999</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>144</v>
       </c>
       <c r="B163" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C163">
         <v>162</v>
@@ -3260,12 +3260,12 @@
         <v>0.311</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>156</v>
       </c>
       <c r="B164" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C164">
         <v>163</v>
@@ -3274,12 +3274,12 @@
         <v>3.0306000000000002</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C165">
         <v>164</v>
@@ -3288,12 +3288,12 @@
         <v>0.34429999999999999</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>152</v>
       </c>
       <c r="B166" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C166">
         <v>165</v>
@@ -3302,12 +3302,12 @@
         <v>3.9489999999999998</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>170</v>
       </c>
       <c r="B167" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C167">
         <v>166</v>
@@ -3316,12 +3316,12 @@
         <v>1.0399</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>141</v>
       </c>
       <c r="B168" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C168">
         <v>167</v>
@@ -3330,12 +3330,12 @@
         <v>0.76019999999999999</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>113</v>
       </c>
       <c r="B169" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C169">
         <v>168</v>
@@ -3344,12 +3344,12 @@
         <v>0.95509999999999995</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>167</v>
       </c>
       <c r="B170" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C170">
         <v>169</v>
@@ -3358,12 +3358,12 @@
         <v>0.70540000000000003</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>153</v>
       </c>
       <c r="B171" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C171">
         <v>170</v>
@@ -3372,12 +3372,12 @@
         <v>0.33150000000000002</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>177</v>
       </c>
       <c r="B172" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C172">
         <v>171</v>
@@ -3386,12 +3386,12 @@
         <v>6.9074999999999998</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>137</v>
       </c>
       <c r="B173" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C173">
         <v>172</v>
@@ -3400,12 +3400,12 @@
         <v>1.6666000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>100</v>
       </c>
       <c r="B174" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C174">
         <v>173</v>
@@ -3414,12 +3414,12 @@
         <v>3.9809999999999999</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>178</v>
       </c>
       <c r="B175" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C175">
         <v>174</v>
@@ -3428,12 +3428,12 @@
         <v>3.5082</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>151</v>
       </c>
       <c r="B176" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C176">
         <v>175</v>
@@ -3442,12 +3442,12 @@
         <v>0.34379999999999999</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>149</v>
       </c>
       <c r="B177" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C177">
         <v>176</v>
@@ -3456,12 +3456,12 @@
         <v>0.59960000000000002</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>154</v>
       </c>
       <c r="B178" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C178">
         <v>177</v>
@@ -3470,12 +3470,12 @@
         <v>0.43280000000000002</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>106</v>
       </c>
       <c r="B179" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C179">
         <v>178</v>
@@ -3484,12 +3484,12 @@
         <v>0.64180000000000004</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>183</v>
       </c>
       <c r="B180" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C180">
         <v>179</v>
@@ -3498,12 +3498,12 @@
         <v>5.0457999999999998</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>109</v>
       </c>
       <c r="B181" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C181">
         <v>180</v>
@@ -3512,12 +3512,12 @@
         <v>1.3520000000000001</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C182">
         <v>181</v>
@@ -3526,12 +3526,12 @@
         <v>3.2393000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>160</v>
       </c>
       <c r="B183" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C183">
         <v>182</v>
@@ -3540,12 +3540,12 @@
         <v>3.4826000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>164</v>
       </c>
       <c r="B184" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C184" s="5">
         <v>183</v>
@@ -3554,12 +3554,12 @@
         <v>0.93340000000000001</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>161</v>
       </c>
       <c r="B185" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C185">
         <v>184</v>
@@ -3568,12 +3568,12 @@
         <v>0.86990000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>116</v>
       </c>
       <c r="B186" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C186">
         <v>185</v>
@@ -3582,12 +3582,12 @@
         <v>3.1699999999999999E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>136</v>
       </c>
       <c r="B187" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C187">
         <v>186</v>
@@ -3596,12 +3596,12 @@
         <v>0.219</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>182</v>
       </c>
       <c r="B188" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C188">
         <v>187</v>
@@ -3610,12 +3610,12 @@
         <v>6.7279999999999998</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>135</v>
       </c>
       <c r="B189" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C189">
         <v>188</v>
@@ -3624,12 +3624,12 @@
         <v>0.69350000000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>155</v>
       </c>
       <c r="B190" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C190">
         <v>189</v>
@@ -3638,12 +3638,12 @@
         <v>3.8347000000000002</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>179</v>
       </c>
       <c r="B191" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C191">
         <v>190</v>
@@ -3652,12 +3652,12 @@
         <v>2.5015999999999998</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>168</v>
       </c>
       <c r="B192" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C192">
         <v>191</v>
@@ -3666,12 +3666,12 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>108</v>
       </c>
       <c r="B193" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C193">
         <v>192</v>
@@ -3680,12 +3680,12 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>150</v>
       </c>
       <c r="B194" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C194">
         <v>193</v>
@@ -3694,12 +3694,12 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>133</v>
       </c>
       <c r="B195" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C195">
         <v>194</v>
@@ -3708,12 +3708,12 @@
         <v>2.6573000000000002</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>181</v>
       </c>
       <c r="B196" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C196">
         <v>195</v>
@@ -3722,12 +3722,12 @@
         <v>5.1012000000000004</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>295</v>
       </c>
       <c r="B197" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C197">
         <v>196</v>
@@ -3736,12 +3736,12 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>134</v>
       </c>
       <c r="B198" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C198">
         <v>197</v>
@@ -3750,12 +3750,12 @@
         <v>4.1407999999999996</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>286</v>
       </c>
       <c r="B199" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C199">
         <v>198</v>
@@ -3764,12 +3764,12 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>299</v>
       </c>
       <c r="B200" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C200">
         <v>199</v>
@@ -3778,12 +3778,12 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>206</v>
       </c>
       <c r="B201" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C201">
         <v>200</v>
@@ -3792,12 +3792,12 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>214</v>
       </c>
       <c r="B202" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C202">
         <v>201</v>
@@ -3806,12 +3806,12 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>221</v>
       </c>
       <c r="B203" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C203">
         <v>202</v>
@@ -3820,12 +3820,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>257</v>
       </c>
       <c r="B204" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C204">
         <v>203</v>
@@ -3834,12 +3834,12 @@
         <v>10.78</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>237</v>
       </c>
       <c r="B205" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C205">
         <v>204</v>
@@ -3848,12 +3848,12 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>210</v>
       </c>
       <c r="B206" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C206">
         <v>205</v>
@@ -3862,12 +3862,12 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>251</v>
       </c>
       <c r="B207" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C207">
         <v>206</v>
@@ -3876,12 +3876,12 @@
         <v>10.76</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>196</v>
       </c>
       <c r="B208" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C208">
         <v>207</v>
@@ -3890,12 +3890,12 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>187</v>
       </c>
       <c r="B209" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C209">
         <v>208</v>
@@ -3904,12 +3904,12 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>256</v>
       </c>
       <c r="B210" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C210">
         <v>209</v>
@@ -3918,12 +3918,12 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>204</v>
       </c>
       <c r="B211" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C211">
         <v>210</v>
@@ -3932,12 +3932,12 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>193</v>
       </c>
       <c r="B212" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C212">
         <v>211</v>
@@ -3946,12 +3946,12 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>260</v>
       </c>
       <c r="B213" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C213">
         <v>212</v>
@@ -3960,12 +3960,12 @@
         <v>11.45</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>284</v>
       </c>
       <c r="B214" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C214">
         <v>213</v>
@@ -3974,12 +3974,12 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>277</v>
       </c>
       <c r="B215" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C215">
         <v>214</v>
@@ -3988,12 +3988,12 @@
         <v>13.09</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>235</v>
       </c>
       <c r="B216" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C216">
         <v>215</v>
@@ -4002,12 +4002,12 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>241</v>
       </c>
       <c r="B217" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C217">
         <v>216</v>
@@ -4016,12 +4016,12 @@
         <v>6.64</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>252</v>
       </c>
       <c r="B218" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C218">
         <v>217</v>
@@ -4030,12 +4030,12 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>261</v>
       </c>
       <c r="B219" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C219">
         <v>218</v>
@@ -4044,12 +4044,12 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>201</v>
       </c>
       <c r="B220" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C220">
         <v>219</v>
@@ -4058,12 +4058,12 @@
         <v>9.89</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>239</v>
       </c>
       <c r="B221" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C221">
         <v>220</v>
@@ -4072,12 +4072,12 @@
         <v>11.02</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>250</v>
       </c>
       <c r="B222" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C222">
         <v>221</v>
@@ -4086,12 +4086,12 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>227</v>
       </c>
       <c r="B223" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C223">
         <v>222</v>
@@ -4100,12 +4100,12 @@
         <v>12.78</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>244</v>
       </c>
       <c r="B224" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C224">
         <v>223</v>
@@ -4114,12 +4114,12 @@
         <v>7.24</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>212</v>
       </c>
       <c r="B225" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C225">
         <v>224</v>
@@ -4128,12 +4128,12 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>271</v>
       </c>
       <c r="B226" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C226">
         <v>225</v>
@@ -4142,12 +4142,12 @@
         <v>0.26979999999999998</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>192</v>
       </c>
       <c r="B227" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C227">
         <v>226</v>
@@ -4156,12 +4156,12 @@
         <v>0.1842</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>202</v>
       </c>
       <c r="B228" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C228">
         <v>227</v>
@@ -4170,12 +4170,12 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>298</v>
       </c>
       <c r="B229" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C229">
         <v>228</v>
@@ -4184,12 +4184,12 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>200</v>
       </c>
       <c r="B230" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C230">
         <v>229</v>
@@ -4198,12 +4198,12 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>205</v>
       </c>
       <c r="B231" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C231">
         <v>230</v>
@@ -4212,12 +4212,12 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>223</v>
       </c>
       <c r="B232" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C232">
         <v>231</v>
@@ -4226,12 +4226,12 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>215</v>
       </c>
       <c r="B233" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C233">
         <v>232</v>
@@ -4240,12 +4240,12 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>255</v>
       </c>
       <c r="B234" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C234">
         <v>233</v>
@@ -4254,12 +4254,12 @@
         <v>0.98150000000000004</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>219</v>
       </c>
       <c r="B235" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C235">
         <v>234</v>
@@ -4268,12 +4268,12 @@
         <v>0.30459999999999998</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>233</v>
       </c>
       <c r="B236" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C236">
         <v>235</v>
@@ -4282,12 +4282,12 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>254</v>
       </c>
       <c r="B237" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C237">
         <v>236</v>
@@ -4296,12 +4296,12 @@
         <v>0.98240000000000005</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>259</v>
       </c>
       <c r="B238" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C238">
         <v>237</v>
@@ -4310,12 +4310,12 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>248</v>
       </c>
       <c r="B239" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C239">
         <v>238</v>
@@ -4324,12 +4324,12 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>240</v>
       </c>
       <c r="B240" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C240">
         <v>239</v>
@@ -4338,12 +4338,12 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>198</v>
       </c>
       <c r="B241" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C241">
         <v>240</v>
@@ -4352,12 +4352,12 @@
         <v>0.82740000000000002</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>225</v>
       </c>
       <c r="B242" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C242">
         <v>241</v>
@@ -4366,12 +4366,12 @@
         <v>0.1172</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>222</v>
       </c>
       <c r="B243" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C243">
         <v>242</v>
@@ -4380,12 +4380,12 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>247</v>
       </c>
       <c r="B244" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C244">
         <v>243</v>
@@ -4394,12 +4394,12 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>226</v>
       </c>
       <c r="B245" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C245">
         <v>244</v>
@@ -4408,12 +4408,12 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>209</v>
       </c>
       <c r="B246" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C246">
         <v>245</v>
@@ -4422,12 +4422,12 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>232</v>
       </c>
       <c r="B247" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C247">
         <v>246</v>
@@ -4436,12 +4436,12 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>211</v>
       </c>
       <c r="B248" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C248">
         <v>247</v>
@@ -4450,12 +4450,12 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>253</v>
       </c>
       <c r="B249" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C249">
         <v>248</v>
@@ -4464,12 +4464,12 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>203</v>
       </c>
       <c r="B250" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C250">
         <v>249</v>
@@ -4478,12 +4478,12 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>274</v>
       </c>
       <c r="B251" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C251">
         <v>250</v>
@@ -4492,12 +4492,12 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>234</v>
       </c>
       <c r="B252" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C252">
         <v>251</v>
@@ -4506,12 +4506,12 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>272</v>
       </c>
       <c r="B253" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C253">
         <v>252</v>
@@ -4520,12 +4520,12 @@
         <v>0.99070000000000003</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>207</v>
       </c>
       <c r="B254" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C254">
         <v>253</v>
@@ -4534,12 +4534,12 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>228</v>
       </c>
       <c r="B255" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C255">
         <v>254</v>
@@ -4548,12 +4548,12 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>266</v>
       </c>
       <c r="B256" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C256">
         <v>255</v>
@@ -4562,12 +4562,12 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>269</v>
       </c>
       <c r="B257" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C257">
         <v>256</v>
@@ -4576,12 +4576,12 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>275</v>
       </c>
       <c r="B258" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C258">
         <v>257</v>
@@ -4590,12 +4590,12 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>278</v>
       </c>
       <c r="B259" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C259">
         <v>258</v>
@@ -4604,12 +4604,12 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>245</v>
       </c>
       <c r="B260" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C260">
         <v>259</v>
@@ -4618,12 +4618,12 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>185</v>
       </c>
       <c r="B261" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C261">
         <v>260</v>
@@ -4632,12 +4632,12 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>273</v>
       </c>
       <c r="B262" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C262">
         <v>261</v>
@@ -4646,12 +4646,12 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>264</v>
       </c>
       <c r="B263" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C263">
         <v>262</v>
@@ -4660,12 +4660,12 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>300</v>
       </c>
       <c r="B264" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C264">
         <v>263</v>
@@ -4674,12 +4674,12 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>238</v>
       </c>
       <c r="B265" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C265">
         <v>264</v>
@@ -4688,12 +4688,12 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>199</v>
       </c>
       <c r="B266" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C266">
         <v>265</v>
@@ -4702,12 +4702,12 @@
         <v>10.14</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>236</v>
       </c>
       <c r="B267" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C267">
         <v>266</v>
@@ -4716,12 +4716,12 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>217</v>
       </c>
       <c r="B268" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C268">
         <v>267</v>
@@ -4730,12 +4730,12 @@
         <v>10.36</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>190</v>
       </c>
       <c r="B269" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C269">
         <v>268</v>
@@ -4744,12 +4744,12 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>186</v>
       </c>
       <c r="B270" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C270">
         <v>269</v>
@@ -4758,12 +4758,12 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>220</v>
       </c>
       <c r="B271" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C271">
         <v>270</v>
@@ -4772,12 +4772,12 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>216</v>
       </c>
       <c r="B272" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C272">
         <v>271</v>
@@ -4786,12 +4786,12 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>282</v>
       </c>
       <c r="B273" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C273">
         <v>272</v>
@@ -4800,12 +4800,12 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>230</v>
       </c>
       <c r="B274" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C274">
         <v>273</v>
@@ -4814,12 +4814,12 @@
         <v>0.15440000000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>268</v>
       </c>
       <c r="B275" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C275">
         <v>274</v>
@@ -4828,12 +4828,12 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>285</v>
       </c>
       <c r="B276" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C276">
         <v>275</v>
@@ -4842,12 +4842,12 @@
         <v>9.9169999999999998</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>197</v>
       </c>
       <c r="B277" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C277">
         <v>276</v>
@@ -4856,12 +4856,12 @@
         <v>14.26</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>229</v>
       </c>
       <c r="B278" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C278">
         <v>277</v>
@@ -4870,12 +4870,12 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>188</v>
       </c>
       <c r="B279" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C279">
         <v>278</v>
@@ -4884,12 +4884,12 @@
         <v>12.08</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>213</v>
       </c>
       <c r="B280" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C280">
         <v>279</v>
@@ -4898,12 +4898,12 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C281">
         <v>280</v>
@@ -4912,12 +4912,12 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>265</v>
       </c>
       <c r="B282" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C282">
         <v>281</v>
@@ -4926,12 +4926,12 @@
         <v>13.44</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C283">
         <v>282</v>
@@ -4940,12 +4940,12 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>242</v>
       </c>
       <c r="B284" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C284">
         <v>283</v>
@@ -4954,12 +4954,12 @@
         <v>10.57</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>258</v>
       </c>
       <c r="B285" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C285">
         <v>284</v>
@@ -4968,12 +4968,12 @@
         <v>14.18</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>195</v>
       </c>
       <c r="B286" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C286">
         <v>285</v>
@@ -4982,12 +4982,12 @@
         <v>10.32</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>184</v>
       </c>
       <c r="B287" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C287">
         <v>286</v>
@@ -4996,12 +4996,12 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>208</v>
       </c>
       <c r="B288" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C288">
         <v>287</v>
@@ -5010,12 +5010,12 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>270</v>
       </c>
       <c r="B289" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C289">
         <v>288</v>
@@ -5024,12 +5024,12 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>280</v>
       </c>
       <c r="B290" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C290">
         <v>289</v>
@@ -5038,12 +5038,12 @@
         <v>0.72499999999999998</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>191</v>
       </c>
       <c r="B291" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C291">
         <v>290</v>
@@ -5052,12 +5052,12 @@
         <v>0.1051</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>263</v>
       </c>
       <c r="B292" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C292">
         <v>291</v>
@@ -5066,12 +5066,12 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>194</v>
       </c>
       <c r="B293" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C293">
         <v>292</v>
@@ -5080,12 +5080,12 @@
         <v>0.19869999999999999</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>246</v>
       </c>
       <c r="B294" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C294">
         <v>293</v>
@@ -5094,12 +5094,12 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>249</v>
       </c>
       <c r="B295" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C295">
         <v>294</v>
@@ -5108,12 +5108,12 @@
         <v>1.7345999999999999</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>231</v>
       </c>
       <c r="B296" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C296">
         <v>295</v>
@@ -5122,12 +5122,12 @@
         <v>0.26550000000000001</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>224</v>
       </c>
       <c r="B297" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C297">
         <v>296</v>
@@ -5136,12 +5136,12 @@
         <v>0.22589999999999999</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>243</v>
       </c>
       <c r="B298" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C298">
         <v>297</v>
@@ -5150,12 +5150,12 @@
         <v>3.8199999999999998E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>262</v>
       </c>
       <c r="B299" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C299">
         <v>298</v>
@@ -5164,12 +5164,12 @@
         <v>0.1191</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>218</v>
       </c>
       <c r="B300" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C300">
         <v>299</v>
@@ -5178,12 +5178,12 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>267</v>
       </c>
       <c r="B301" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C301">
         <v>300</v>
@@ -5192,12 +5192,12 @@
         <v>0.129</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>357</v>
       </c>
       <c r="B302" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C302">
         <v>301</v>
@@ -5206,12 +5206,12 @@
         <v>1.3434999999999999</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>316</v>
       </c>
       <c r="B303" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C303">
         <v>302</v>
@@ -5220,12 +5220,12 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>307</v>
       </c>
       <c r="B304" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C304">
         <v>303</v>
@@ -5234,12 +5234,12 @@
         <v>1.8599999999999998E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>306</v>
       </c>
       <c r="B305" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C305">
         <v>304</v>
@@ -5248,12 +5248,12 @@
         <v>0.2268</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>332</v>
       </c>
       <c r="B306" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C306">
         <v>305</v>
@@ -5262,12 +5262,12 @@
         <v>0.14990000000000001</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>326</v>
       </c>
       <c r="B307" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C307">
         <v>306</v>
@@ -5276,12 +5276,12 @@
         <v>8.8099999999999998E-2</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>301</v>
       </c>
       <c r="B308" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C308">
         <v>307</v>
@@ -5290,12 +5290,12 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>330</v>
       </c>
       <c r="B309" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C309">
         <v>308</v>
@@ -5304,12 +5304,12 @@
         <v>0.37169999999999997</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>321</v>
       </c>
       <c r="B310" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C310">
         <v>309</v>
@@ -5318,12 +5318,12 @@
         <v>2.1137999999999999</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>378</v>
       </c>
       <c r="B311" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C311">
         <v>310</v>
@@ -5332,12 +5332,12 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>339</v>
       </c>
       <c r="B312" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C312">
         <v>311</v>
@@ -5346,12 +5346,12 @@
         <v>4.4299999999999999E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>328</v>
       </c>
       <c r="B313" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C313">
         <v>312</v>
@@ -5360,12 +5360,12 @@
         <v>0.62790000000000001</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>335</v>
       </c>
       <c r="B314" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C314">
         <v>313</v>
@@ -5374,12 +5374,12 @@
         <v>0.52400000000000002</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C315">
         <v>314</v>
@@ -5388,12 +5388,12 @@
         <v>0.25559999999999999</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>345</v>
       </c>
       <c r="B316" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C316">
         <v>315</v>
@@ -5402,12 +5402,12 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>308</v>
       </c>
       <c r="B317" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C317">
         <v>316</v>
@@ -5416,12 +5416,12 @@
         <v>1.9300000000000001E-2</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>329</v>
       </c>
       <c r="B318" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C318">
         <v>317</v>
@@ -5430,12 +5430,12 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>363</v>
       </c>
       <c r="B319" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C319">
         <v>318</v>
@@ -5444,12 +5444,12 @@
         <v>0.628</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>337</v>
       </c>
       <c r="B320" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C320">
         <v>319</v>
@@ -5458,12 +5458,12 @@
         <v>0.30549999999999999</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C321">
         <v>320</v>
@@ -5472,12 +5472,12 @@
         <v>0.19769999999999999</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>313</v>
       </c>
       <c r="B322" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C322">
         <v>321</v>
@@ -5486,12 +5486,12 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>338</v>
       </c>
       <c r="B323" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C323">
         <v>322</v>
@@ -5500,12 +5500,12 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>347</v>
       </c>
       <c r="B324" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C324">
         <v>323</v>
@@ -5514,12 +5514,12 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>372</v>
       </c>
       <c r="B325" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C325">
         <v>324</v>
@@ -5528,12 +5528,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>354</v>
       </c>
       <c r="B326" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C326">
         <v>325</v>
@@ -5542,12 +5542,12 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>343</v>
       </c>
       <c r="B327" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C327">
         <v>326</v>
@@ -5556,12 +5556,12 @@
         <v>3.1993</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>303</v>
       </c>
       <c r="B328" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C328">
         <v>327</v>
@@ -5570,12 +5570,12 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>310</v>
       </c>
       <c r="B329" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C329">
         <v>328</v>
@@ -5584,12 +5584,12 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>348</v>
       </c>
       <c r="B330" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C330">
         <v>329</v>
@@ -5598,12 +5598,12 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>315</v>
       </c>
       <c r="B331" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C331">
         <v>330</v>
@@ -5612,12 +5612,12 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>375</v>
       </c>
       <c r="B332" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C332">
         <v>331</v>
@@ -5626,12 +5626,12 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>352</v>
       </c>
       <c r="B333" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C333">
         <v>332</v>
@@ -5640,15 +5640,15 @@
         <v>16.75</v>
       </c>
       <c r="E333" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>309</v>
       </c>
       <c r="B334" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C334">
         <v>333</v>
@@ -5657,12 +5657,12 @@
         <v>8.1803000000000008</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>317</v>
       </c>
       <c r="B335" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C335">
         <v>334</v>
@@ -5671,12 +5671,12 @@
         <v>14.62</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>369</v>
       </c>
       <c r="B336" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C336">
         <v>335</v>
@@ -5685,12 +5685,12 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>353</v>
       </c>
       <c r="B337" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C337">
         <v>336</v>
@@ -5699,12 +5699,12 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>351</v>
       </c>
       <c r="B338" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C338">
         <v>337</v>
@@ -5713,12 +5713,12 @@
         <v>8.1199999999999992</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>327</v>
       </c>
       <c r="B339" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C339">
         <v>338</v>
@@ -5727,12 +5727,12 @@
         <v>11.48</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>376</v>
       </c>
       <c r="B340" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C340">
         <v>339</v>
@@ -5741,12 +5741,12 @@
         <v>8.32</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>366</v>
       </c>
       <c r="B341" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C341">
         <v>340</v>
@@ -5755,12 +5755,12 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>365</v>
       </c>
       <c r="B342" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C342">
         <v>341</v>
@@ -5769,12 +5769,12 @@
         <v>8.68</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>379</v>
       </c>
       <c r="B343" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C343">
         <v>342</v>
@@ -5783,12 +5783,12 @@
         <v>11.77</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>377</v>
       </c>
       <c r="B344" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C344">
         <v>343</v>
@@ -5797,12 +5797,12 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>361</v>
       </c>
       <c r="B345" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C345">
         <v>344</v>
@@ -5811,12 +5811,12 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>340</v>
       </c>
       <c r="B346" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C346">
         <v>345</v>
@@ -5825,12 +5825,12 @@
         <v>7.99</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>305</v>
       </c>
       <c r="B347" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C347">
         <v>346</v>
@@ -5839,12 +5839,12 @@
         <v>9.2100000000000009</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>371</v>
       </c>
       <c r="B348" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C348">
         <v>347</v>
@@ -5853,12 +5853,12 @@
         <v>11.77</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>356</v>
       </c>
       <c r="B349" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C349">
         <v>348</v>
@@ -5867,12 +5867,12 @@
         <v>12.83</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>333</v>
       </c>
       <c r="B350" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C350">
         <v>349</v>
@@ -5881,12 +5881,12 @@
         <v>9.2899999999999991</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>319</v>
       </c>
       <c r="B351" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C351">
         <v>350</v>
@@ -5895,12 +5895,12 @@
         <v>14.44</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>360</v>
       </c>
       <c r="B352" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C352">
         <v>351</v>
@@ -5909,12 +5909,12 @@
         <v>7.11</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>359</v>
       </c>
       <c r="B353" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C353">
         <v>352</v>
@@ -5923,12 +5923,12 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>331</v>
       </c>
       <c r="B354" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C354">
         <v>353</v>
@@ -5937,12 +5937,12 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>323</v>
       </c>
       <c r="B355" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C355">
         <v>354</v>
@@ -5951,12 +5951,12 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>334</v>
       </c>
       <c r="B356" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C356">
         <v>355</v>
@@ -5965,12 +5965,12 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>374</v>
       </c>
       <c r="B357" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C357">
         <v>356</v>
@@ -5979,12 +5979,12 @@
         <v>0.378</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>367</v>
       </c>
       <c r="B358" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C358">
         <v>357</v>
@@ -5993,12 +5993,12 @@
         <v>1.0821000000000001</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C359">
         <v>358</v>
@@ -6007,12 +6007,12 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>322</v>
       </c>
       <c r="B360" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C360">
         <v>359</v>
@@ -6021,12 +6021,12 @@
         <v>0.80520000000000003</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>336</v>
       </c>
       <c r="B361" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C361">
         <v>360</v>
@@ -6035,12 +6035,12 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>383</v>
       </c>
       <c r="B362" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C362">
         <v>361</v>
@@ -6049,12 +6049,12 @@
         <v>8.7099999999999997E-2</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>318</v>
       </c>
       <c r="B363" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C363">
         <v>362</v>
@@ -6063,12 +6063,12 @@
         <v>7.9600000000000004E-2</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>368</v>
       </c>
       <c r="B364" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C364">
         <v>363</v>
@@ -6077,12 +6077,12 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>355</v>
       </c>
       <c r="B365" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C365">
         <v>364</v>
@@ -6091,12 +6091,12 @@
         <v>0.82930000000000004</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>370</v>
       </c>
       <c r="B366" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C366">
         <v>365</v>
@@ -6105,12 +6105,12 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>346</v>
       </c>
       <c r="B367" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C367">
         <v>366</v>
@@ -6119,12 +6119,12 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>362</v>
       </c>
       <c r="B368" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C368">
         <v>367</v>
@@ -6133,12 +6133,12 @@
         <v>0.2475</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>380</v>
       </c>
       <c r="B369" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C369">
         <v>368</v>
@@ -6147,12 +6147,12 @@
         <v>0.35570000000000002</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>344</v>
       </c>
       <c r="B370" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C370">
         <v>369</v>
@@ -6161,12 +6161,12 @@
         <v>0.42470000000000002</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>325</v>
       </c>
       <c r="B371" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C371">
         <v>370</v>
@@ -6175,12 +6175,12 @@
         <v>0.1948</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>350</v>
       </c>
       <c r="B372" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C372">
         <v>371</v>
@@ -6189,12 +6189,12 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>312</v>
       </c>
       <c r="B373" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C373">
         <v>372</v>
@@ -6203,12 +6203,12 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>364</v>
       </c>
       <c r="B374" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C374">
         <v>373</v>
@@ -6217,12 +6217,12 @@
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>311</v>
       </c>
       <c r="B375" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C375">
         <v>374</v>
@@ -6231,12 +6231,12 @@
         <v>12.061</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>341</v>
       </c>
       <c r="B376" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C376">
         <v>376</v>
@@ -6245,12 +6245,12 @@
         <v>0.64300000000000002</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>342</v>
       </c>
       <c r="B377" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C377">
         <v>377</v>
@@ -6259,12 +6259,12 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>382</v>
       </c>
       <c r="B378" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C378">
         <v>378</v>
@@ -6273,12 +6273,12 @@
         <v>0.3972</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>302</v>
       </c>
       <c r="B379" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C379">
         <v>379</v>
@@ -6287,12 +6287,12 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>381</v>
       </c>
       <c r="B380" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C380">
         <v>380</v>
@@ -6301,12 +6301,12 @@
         <v>0.13800000000000001</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>373</v>
       </c>
       <c r="B381" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C381">
         <v>381</v>
@@ -6315,12 +6315,12 @@
         <v>1.5334000000000001</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>349</v>
       </c>
       <c r="B382" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C382">
         <v>382</v>
@@ -6329,12 +6329,12 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>304</v>
       </c>
       <c r="B383" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C383">
         <v>383</v>
@@ -6343,12 +6343,12 @@
         <v>0.62990000000000002</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>324</v>
       </c>
       <c r="B384" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C384">
         <v>384</v>
@@ -6378,14 +6378,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E607A91-5784-49B2-9D72-3E3DD9AE54DA}">
   <dimension ref="D3:F387"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D4">
         <v>1</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>2</v>
       </c>
@@ -6401,7 +6401,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D6">
         <v>3</v>
       </c>
@@ -6409,7 +6409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7">
         <v>4</v>
       </c>
@@ -6417,7 +6417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8">
         <v>5</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D9">
         <v>6</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D10">
         <v>7</v>
       </c>
@@ -6441,7 +6441,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D11">
         <v>8</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D12">
         <v>9</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D13">
         <v>10</v>
       </c>
@@ -6465,7 +6465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D14">
         <v>11</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D15">
         <v>12</v>
       </c>
@@ -6481,7 +6481,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <v>13</v>
       </c>
@@ -6489,7 +6489,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D17">
         <v>14</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D18">
         <v>15</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D19">
         <v>16</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D20">
         <v>17</v>
       </c>
@@ -6521,7 +6521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D21">
         <v>18</v>
       </c>
@@ -6529,7 +6529,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D22">
         <v>19</v>
       </c>
@@ -6537,7 +6537,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D23">
         <v>20</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D24">
         <v>21</v>
       </c>
@@ -6553,7 +6553,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D25">
         <v>22</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D26">
         <v>23</v>
       </c>
@@ -6569,7 +6569,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D27">
         <v>24</v>
       </c>
@@ -6577,7 +6577,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D28">
         <v>25</v>
       </c>
@@ -6585,7 +6585,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D29">
         <v>26</v>
       </c>
@@ -6593,7 +6593,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D30">
         <v>27</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D31">
         <v>28</v>
       </c>
@@ -6609,7 +6609,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D32">
         <v>29</v>
       </c>
@@ -6617,7 +6617,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D33">
         <v>30</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D34">
         <v>31</v>
       </c>
@@ -6633,7 +6633,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D35">
         <v>32</v>
       </c>
@@ -6641,7 +6641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D36">
         <v>33</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D37">
         <v>34</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D38">
         <v>35</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D39">
         <v>36</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D40">
         <v>37</v>
       </c>
@@ -6681,7 +6681,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D41">
         <v>38</v>
       </c>
@@ -6689,7 +6689,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D42">
         <v>39</v>
       </c>
@@ -6697,7 +6697,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D43">
         <v>40</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D44">
         <v>41</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D45">
         <v>42</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D46">
         <v>43</v>
       </c>
@@ -6729,7 +6729,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D47">
         <v>44</v>
       </c>
@@ -6737,7 +6737,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D48">
         <v>45</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D49">
         <v>46</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D50">
         <v>47</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D51">
         <v>48</v>
       </c>
@@ -6769,7 +6769,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D52">
         <v>49</v>
       </c>
@@ -6777,7 +6777,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D53">
         <v>50</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D54">
         <v>51</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D55">
         <v>52</v>
       </c>
@@ -6801,7 +6801,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="56" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D56">
         <v>53</v>
       </c>
@@ -6809,7 +6809,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D57">
         <v>54</v>
       </c>
@@ -6817,7 +6817,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D58">
         <v>55</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D59">
         <v>56</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D60">
         <v>57</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D61">
         <v>58</v>
       </c>
@@ -6849,7 +6849,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D62">
         <v>59</v>
       </c>
@@ -6857,7 +6857,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D63">
         <v>60</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D64">
         <v>61</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D65">
         <v>62</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D66">
         <v>63</v>
       </c>
@@ -6889,7 +6889,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D67">
         <v>64</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D68">
         <v>65</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D69">
         <v>66</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D70">
         <v>67</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D71">
         <v>68</v>
       </c>
@@ -6929,7 +6929,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="72" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D72">
         <v>69</v>
       </c>
@@ -6937,7 +6937,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D73">
         <v>70</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D74">
         <v>71</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="75" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D75">
         <v>72</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="76" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D76">
         <v>73</v>
       </c>
@@ -6969,7 +6969,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="77" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D77">
         <v>74</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="78" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D78">
         <v>75</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D79">
         <v>76</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D80">
         <v>77</v>
       </c>
@@ -7001,7 +7001,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="81" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D81">
         <v>78</v>
       </c>
@@ -7009,7 +7009,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="82" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D82">
         <v>79</v>
       </c>
@@ -7017,7 +7017,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D83">
         <v>80</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="84" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D84">
         <v>81</v>
       </c>
@@ -7033,7 +7033,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="85" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D85">
         <v>82</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="86" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D86">
         <v>83</v>
       </c>
@@ -7049,7 +7049,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="87" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D87">
         <v>84</v>
       </c>
@@ -7057,7 +7057,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="88" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D88">
         <v>85</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D89">
         <v>86</v>
       </c>
@@ -7073,7 +7073,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="90" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D90">
         <v>87</v>
       </c>
@@ -7081,7 +7081,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="91" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D91">
         <v>88</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="92" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D92">
         <v>89</v>
       </c>
@@ -7097,7 +7097,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="93" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D93">
         <v>90</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D94">
         <v>91</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="95" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D95">
         <v>92</v>
       </c>
@@ -7121,7 +7121,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="96" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D96">
         <v>93</v>
       </c>
@@ -7129,7 +7129,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="97" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D97">
         <v>94</v>
       </c>
@@ -7137,7 +7137,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="98" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D98">
         <v>95</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="99" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D99">
         <v>96</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="100" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D100">
         <v>97</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="101" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D101">
         <v>98</v>
       </c>
@@ -7169,7 +7169,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="102" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D102">
         <v>99</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="103" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D103">
         <v>100</v>
       </c>
@@ -7185,7 +7185,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="104" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D104">
         <v>101</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="105" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D105">
         <v>102</v>
       </c>
@@ -7201,7 +7201,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="106" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D106">
         <v>103</v>
       </c>
@@ -7209,7 +7209,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="107" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D107">
         <v>104</v>
       </c>
@@ -7217,7 +7217,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="108" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D108">
         <v>105</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="109" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D109">
         <v>106</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="110" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D110">
         <v>107</v>
       </c>
@@ -7241,7 +7241,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D111">
         <v>108</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="112" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D112">
         <v>109</v>
       </c>
@@ -7257,7 +7257,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="113" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D113">
         <v>110</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="114" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D114">
         <v>111</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="115" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D115">
         <v>112</v>
       </c>
@@ -7281,7 +7281,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="116" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D116">
         <v>113</v>
       </c>
@@ -7289,7 +7289,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="117" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D117">
         <v>114</v>
       </c>
@@ -7297,7 +7297,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="118" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D118">
         <v>115</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="119" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D119">
         <v>116</v>
       </c>
@@ -7313,7 +7313,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="120" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D120">
         <v>117</v>
       </c>
@@ -7321,7 +7321,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="121" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D121">
         <v>118</v>
       </c>
@@ -7329,7 +7329,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="122" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D122">
         <v>119</v>
       </c>
@@ -7337,7 +7337,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="123" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D123">
         <v>120</v>
       </c>
@@ -7345,7 +7345,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="124" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D124">
         <v>121</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="125" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D125">
         <v>122</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="126" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D126">
         <v>123</v>
       </c>
@@ -7369,7 +7369,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="127" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D127">
         <v>124</v>
       </c>
@@ -7377,7 +7377,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="128" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D128">
         <v>125</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="129" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D129">
         <v>126</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="130" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D130">
         <v>127</v>
       </c>
@@ -7401,7 +7401,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="131" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D131">
         <v>128</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="132" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D132">
         <v>129</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="133" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D133">
         <v>130</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="134" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D134">
         <v>131</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="135" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D135">
         <v>132</v>
       </c>
@@ -7441,7 +7441,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="136" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D136">
         <v>133</v>
       </c>
@@ -7449,7 +7449,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="137" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D137">
         <v>134</v>
       </c>
@@ -7457,7 +7457,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="138" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D138">
         <v>135</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="139" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D139">
         <v>136</v>
       </c>
@@ -7473,7 +7473,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="140" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D140">
         <v>137</v>
       </c>
@@ -7481,7 +7481,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="141" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D141">
         <v>138</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="142" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D142">
         <v>139</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="143" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D143">
         <v>140</v>
       </c>
@@ -7505,7 +7505,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="144" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D144">
         <v>141</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="145" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D145">
         <v>142</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="146" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D146">
         <v>143</v>
       </c>
@@ -7529,7 +7529,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="147" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D147">
         <v>144</v>
       </c>
@@ -7537,7 +7537,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="148" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D148">
         <v>145</v>
       </c>
@@ -7545,7 +7545,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="149" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D149">
         <v>146</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="150" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D150">
         <v>147</v>
       </c>
@@ -7561,7 +7561,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="151" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D151">
         <v>148</v>
       </c>
@@ -7569,7 +7569,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="152" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D152">
         <v>149</v>
       </c>
@@ -7577,7 +7577,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="153" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D153">
         <v>150</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="154" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D154">
         <v>151</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="155" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D155">
         <v>152</v>
       </c>
@@ -7601,7 +7601,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="156" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D156">
         <v>153</v>
       </c>
@@ -7609,7 +7609,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="157" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D157">
         <v>154</v>
       </c>
@@ -7617,7 +7617,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="158" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D158">
         <v>155</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="159" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D159">
         <v>156</v>
       </c>
@@ -7633,7 +7633,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="160" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D160">
         <v>157</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="161" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D161">
         <v>158</v>
       </c>
@@ -7649,7 +7649,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="162" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D162">
         <v>159</v>
       </c>
@@ -7657,7 +7657,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="163" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D163">
         <v>160</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="164" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D164">
         <v>161</v>
       </c>
@@ -7673,7 +7673,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="165" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D165">
         <v>162</v>
       </c>
@@ -7681,7 +7681,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="166" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D166">
         <v>163</v>
       </c>
@@ -7689,7 +7689,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="167" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D167">
         <v>164</v>
       </c>
@@ -7697,7 +7697,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="168" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D168">
         <v>165</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="169" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D169">
         <v>166</v>
       </c>
@@ -7713,7 +7713,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="170" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D170">
         <v>167</v>
       </c>
@@ -7721,7 +7721,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="171" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D171">
         <v>168</v>
       </c>
@@ -7729,7 +7729,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="172" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D172">
         <v>169</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="173" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D173">
         <v>170</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="174" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D174">
         <v>171</v>
       </c>
@@ -7753,7 +7753,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="175" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D175">
         <v>172</v>
       </c>
@@ -7761,7 +7761,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="176" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D176">
         <v>173</v>
       </c>
@@ -7769,7 +7769,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="177" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D177">
         <v>174</v>
       </c>
@@ -7777,7 +7777,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="178" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D178">
         <v>175</v>
       </c>
@@ -7785,7 +7785,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="179" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D179">
         <v>176</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="180" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D180">
         <v>177</v>
       </c>
@@ -7801,7 +7801,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="181" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D181">
         <v>178</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="182" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D182">
         <v>179</v>
       </c>
@@ -7817,7 +7817,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="183" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D183">
         <v>180</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="184" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D184">
         <v>181</v>
       </c>
@@ -7833,7 +7833,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="185" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D185">
         <v>182</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="186" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D186">
         <v>183</v>
       </c>
@@ -7849,7 +7849,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="187" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D187">
         <v>184</v>
       </c>
@@ -7857,7 +7857,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="188" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D188">
         <v>185</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="189" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D189">
         <v>186</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="190" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D190">
         <v>187</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="191" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D191">
         <v>188</v>
       </c>
@@ -7889,7 +7889,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="192" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D192">
         <v>189</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="193" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D193">
         <v>190</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="194" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D194">
         <v>191</v>
       </c>
@@ -7913,7 +7913,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="195" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D195">
         <v>192</v>
       </c>
@@ -7921,7 +7921,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="196" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D196">
         <v>193</v>
       </c>
@@ -7929,7 +7929,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="197" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D197">
         <v>194</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="198" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D198">
         <v>195</v>
       </c>
@@ -7945,7 +7945,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="199" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D199">
         <v>196</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="200" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D200">
         <v>197</v>
       </c>
@@ -7961,7 +7961,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="201" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D201">
         <v>198</v>
       </c>
@@ -7969,7 +7969,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="202" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D202">
         <v>199</v>
       </c>
@@ -7977,7 +7977,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="203" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D203">
         <v>200</v>
       </c>
@@ -7985,7 +7985,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="204" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D204">
         <v>201</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="205" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D205">
         <v>202</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="206" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D206">
         <v>203</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="207" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D207">
         <v>204</v>
       </c>
@@ -8017,7 +8017,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="208" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D208">
         <v>205</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="209" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D209">
         <v>206</v>
       </c>
@@ -8033,7 +8033,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="210" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D210">
         <v>207</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D211">
         <v>208</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D212">
         <v>209</v>
       </c>
@@ -8057,7 +8057,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D213">
         <v>210</v>
       </c>
@@ -8065,7 +8065,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D214">
         <v>211</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D215">
         <v>212</v>
       </c>
@@ -8081,7 +8081,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D216">
         <v>213</v>
       </c>
@@ -8089,7 +8089,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D217">
         <v>214</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D218">
         <v>215</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D219">
         <v>216</v>
       </c>
@@ -8113,7 +8113,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D220">
         <v>217</v>
       </c>
@@ -8121,7 +8121,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D221">
         <v>218</v>
       </c>
@@ -8129,7 +8129,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D222">
         <v>219</v>
       </c>
@@ -8137,7 +8137,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D223">
         <v>220</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D224">
         <v>221</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="225" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D225">
         <v>222</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="226" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D226">
         <v>223</v>
       </c>
@@ -8169,7 +8169,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="227" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D227">
         <v>224</v>
       </c>
@@ -8177,7 +8177,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="228" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D228">
         <v>225</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="229" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D229">
         <v>226</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="230" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D230">
         <v>227</v>
       </c>
@@ -8201,7 +8201,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="231" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D231">
         <v>228</v>
       </c>
@@ -8209,7 +8209,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="232" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D232">
         <v>229</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="233" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D233">
         <v>230</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="234" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D234">
         <v>231</v>
       </c>
@@ -8233,7 +8233,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="235" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D235">
         <v>232</v>
       </c>
@@ -8241,7 +8241,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="236" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D236">
         <v>233</v>
       </c>
@@ -8249,7 +8249,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="237" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D237">
         <v>234</v>
       </c>
@@ -8257,7 +8257,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="238" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D238">
         <v>235</v>
       </c>
@@ -8265,7 +8265,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="239" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D239">
         <v>236</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="240" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D240">
         <v>237</v>
       </c>
@@ -8281,7 +8281,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="241" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D241">
         <v>238</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="242" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D242">
         <v>239</v>
       </c>
@@ -8297,7 +8297,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="243" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D243">
         <v>240</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="244" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D244">
         <v>241</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="245" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D245">
         <v>242</v>
       </c>
@@ -8321,7 +8321,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="246" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D246">
         <v>243</v>
       </c>
@@ -8329,7 +8329,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="247" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D247">
         <v>244</v>
       </c>
@@ -8337,7 +8337,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="248" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D248">
         <v>245</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="249" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D249">
         <v>246</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="250" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D250">
         <v>247</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="251" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D251">
         <v>248</v>
       </c>
@@ -8369,7 +8369,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="252" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D252">
         <v>249</v>
       </c>
@@ -8377,7 +8377,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="253" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D253">
         <v>250</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="254" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D254">
         <v>251</v>
       </c>
@@ -8393,7 +8393,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="255" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D255">
         <v>252</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="256" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D256">
         <v>253</v>
       </c>
@@ -8409,7 +8409,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="257" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D257">
         <v>254</v>
       </c>
@@ -8417,7 +8417,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="258" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D258">
         <v>255</v>
       </c>
@@ -8425,7 +8425,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="259" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D259">
         <v>256</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="260" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D260">
         <v>257</v>
       </c>
@@ -8441,7 +8441,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="261" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D261">
         <v>258</v>
       </c>
@@ -8449,7 +8449,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="262" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D262">
         <v>259</v>
       </c>
@@ -8457,7 +8457,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="263" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D263">
         <v>260</v>
       </c>
@@ -8465,7 +8465,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="264" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D264">
         <v>261</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="265" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D265">
         <v>262</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="266" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D266">
         <v>263</v>
       </c>
@@ -8489,7 +8489,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="267" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D267">
         <v>264</v>
       </c>
@@ -8497,7 +8497,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="268" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D268">
         <v>265</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="269" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D269">
         <v>266</v>
       </c>
@@ -8513,7 +8513,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="270" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D270">
         <v>267</v>
       </c>
@@ -8521,7 +8521,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="271" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D271">
         <v>268</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="272" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D272">
         <v>269</v>
       </c>
@@ -8537,7 +8537,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="273" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D273">
         <v>270</v>
       </c>
@@ -8545,7 +8545,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="274" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D274">
         <v>271</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="275" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D275">
         <v>272</v>
       </c>
@@ -8561,7 +8561,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="276" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D276">
         <v>273</v>
       </c>
@@ -8569,7 +8569,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="277" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D277">
         <v>274</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="278" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D278">
         <v>275</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="279" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D279">
         <v>276</v>
       </c>
@@ -8593,7 +8593,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="280" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D280">
         <v>277</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="281" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D281">
         <v>278</v>
       </c>
@@ -8609,7 +8609,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="282" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D282">
         <v>279</v>
       </c>
@@ -8617,7 +8617,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="283" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D283">
         <v>280</v>
       </c>
@@ -8625,7 +8625,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="284" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D284">
         <v>281</v>
       </c>
@@ -8633,7 +8633,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="285" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D285">
         <v>282</v>
       </c>
@@ -8641,7 +8641,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="286" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D286">
         <v>283</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="287" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D287">
         <v>284</v>
       </c>
@@ -8657,7 +8657,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="288" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D288">
         <v>285</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="289" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D289">
         <v>286</v>
       </c>
@@ -8673,7 +8673,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="290" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D290">
         <v>287</v>
       </c>
@@ -8681,7 +8681,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="291" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D291">
         <v>288</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="292" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D292">
         <v>289</v>
       </c>
@@ -8697,7 +8697,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="293" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D293">
         <v>290</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="294" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D294">
         <v>291</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="295" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D295">
         <v>292</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="296" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D296">
         <v>293</v>
       </c>
@@ -8729,7 +8729,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="297" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D297">
         <v>294</v>
       </c>
@@ -8737,7 +8737,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="298" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D298">
         <v>295</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="299" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D299">
         <v>296</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="300" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D300">
         <v>297</v>
       </c>
@@ -8761,7 +8761,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="301" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D301">
         <v>298</v>
       </c>
@@ -8769,7 +8769,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="302" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D302">
         <v>299</v>
       </c>
@@ -8777,7 +8777,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="303" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D303">
         <v>300</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="304" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D304">
         <v>301</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="305" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D305">
         <v>302</v>
       </c>
@@ -8801,7 +8801,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="306" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D306">
         <v>303</v>
       </c>
@@ -8809,7 +8809,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="307" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D307">
         <v>304</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="308" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D308">
         <v>305</v>
       </c>
@@ -8825,7 +8825,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="309" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D309">
         <v>306</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="310" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D310">
         <v>307</v>
       </c>
@@ -8841,7 +8841,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="311" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D311">
         <v>308</v>
       </c>
@@ -8849,7 +8849,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="312" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D312">
         <v>309</v>
       </c>
@@ -8857,7 +8857,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="313" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D313">
         <v>310</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="314" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D314">
         <v>311</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="315" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D315">
         <v>312</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="316" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D316">
         <v>313</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="317" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D317">
         <v>314</v>
       </c>
@@ -8897,7 +8897,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="318" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D318">
         <v>315</v>
       </c>
@@ -8905,7 +8905,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="319" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D319">
         <v>316</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="320" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D320">
         <v>317</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="321" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D321">
         <v>318</v>
       </c>
@@ -8929,7 +8929,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="322" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D322">
         <v>319</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="323" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D323">
         <v>320</v>
       </c>
@@ -8945,7 +8945,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="324" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D324">
         <v>321</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="325" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D325">
         <v>322</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="326" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D326">
         <v>323</v>
       </c>
@@ -8969,7 +8969,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="327" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D327">
         <v>324</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="328" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D328">
         <v>325</v>
       </c>
@@ -8985,7 +8985,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="329" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D329">
         <v>326</v>
       </c>
@@ -8993,7 +8993,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="330" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D330">
         <v>327</v>
       </c>
@@ -9001,7 +9001,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="331" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D331">
         <v>328</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="332" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D332">
         <v>329</v>
       </c>
@@ -9017,7 +9017,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="333" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D333">
         <v>330</v>
       </c>
@@ -9025,7 +9025,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="334" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D334">
         <v>331</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="335" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D335">
         <v>332</v>
       </c>
@@ -9041,7 +9041,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="336" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D336">
         <v>333</v>
       </c>
@@ -9049,7 +9049,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="337" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D337">
         <v>334</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="338" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D338">
         <v>335</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="339" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D339">
         <v>336</v>
       </c>
@@ -9073,7 +9073,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="340" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D340">
         <v>337</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="341" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D341">
         <v>338</v>
       </c>
@@ -9089,7 +9089,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="342" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D342">
         <v>339</v>
       </c>
@@ -9097,7 +9097,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="343" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D343">
         <v>340</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="344" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D344">
         <v>341</v>
       </c>
@@ -9113,7 +9113,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="345" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D345">
         <v>342</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="346" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D346">
         <v>343</v>
       </c>
@@ -9129,7 +9129,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="347" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D347">
         <v>344</v>
       </c>
@@ -9137,7 +9137,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="348" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D348">
         <v>345</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="349" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D349">
         <v>346</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="350" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D350">
         <v>347</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="351" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D351">
         <v>348</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="352" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D352">
         <v>349</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="353" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D353">
         <v>350</v>
       </c>
@@ -9185,7 +9185,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="354" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D354">
         <v>351</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="355" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D355">
         <v>352</v>
       </c>
@@ -9201,7 +9201,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="356" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D356">
         <v>353</v>
       </c>
@@ -9209,7 +9209,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="357" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D357">
         <v>354</v>
       </c>
@@ -9217,7 +9217,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="358" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D358">
         <v>355</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="359" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D359">
         <v>356</v>
       </c>
@@ -9233,7 +9233,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="360" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D360">
         <v>357</v>
       </c>
@@ -9241,7 +9241,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="361" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D361">
         <v>358</v>
       </c>
@@ -9249,7 +9249,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="362" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D362">
         <v>359</v>
       </c>
@@ -9257,7 +9257,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="363" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D363">
         <v>360</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="364" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D364">
         <v>361</v>
       </c>
@@ -9273,7 +9273,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="365" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D365">
         <v>362</v>
       </c>
@@ -9281,7 +9281,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="366" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D366">
         <v>363</v>
       </c>
@@ -9289,7 +9289,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="367" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D367">
         <v>364</v>
       </c>
@@ -9297,7 +9297,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="368" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D368">
         <v>365</v>
       </c>
@@ -9305,7 +9305,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="369" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D369">
         <v>366</v>
       </c>
@@ -9313,7 +9313,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="370" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D370">
         <v>367</v>
       </c>
@@ -9321,7 +9321,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="371" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D371">
         <v>368</v>
       </c>
@@ -9329,7 +9329,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="372" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D372">
         <v>369</v>
       </c>
@@ -9337,7 +9337,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="373" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D373">
         <v>370</v>
       </c>
@@ -9345,7 +9345,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="374" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D374">
         <v>371</v>
       </c>
@@ -9353,7 +9353,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="375" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D375">
         <v>372</v>
       </c>
@@ -9361,7 +9361,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="376" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D376">
         <v>373</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="377" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D377">
         <v>374</v>
       </c>
@@ -9377,7 +9377,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="378" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D378">
         <v>376</v>
       </c>
@@ -9385,10 +9385,10 @@
         <v>375</v>
       </c>
       <c r="F378" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="379" spans="4:6" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="379" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D379">
         <v>377</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="380" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D380">
         <v>378</v>
       </c>
@@ -9404,7 +9404,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="381" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D381">
         <v>379</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="382" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D382">
         <v>380</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="383" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D383">
         <v>381</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="384" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D384">
         <v>382</v>
       </c>
@@ -9436,7 +9436,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="385" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D385">
         <v>383</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="386" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D386">
         <v>384</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="387" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="4:5" x14ac:dyDescent="0.25">
       <c r="E387">
         <v>384</v>
       </c>
